--- a/Data/Tjoomde.xlsx
+++ b/Data/Tjoomde.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="30.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1718,6 +1718,43 @@
       <c r="G36" s="4" t="inlineStr">
         <is>
           <t>https://tjoomde.my.id/9-PM-Rebel-Sweet-Version</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Hawas Ice - Rasasi</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Hawas Ice</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.fragrantica.com/perfume/Rasasi/Hawas-Ice-89050.html</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Apple, Italian Lemon, Sicilian Bergamot, Star Anise</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Plum, Orange Blossom, Cardamon</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Musk, Amber, Driftwood, Moss</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://tjoomde.my.id/Hawas-Ice</t>
         </is>
       </c>
     </row>
